--- a/Investment Made.xlsx
+++ b/Investment Made.xlsx
@@ -93,7 +93,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,7 +124,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -133,9 +132,11 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -484,9 +485,10 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col width="18.44140625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="13.44140625" bestFit="1" customWidth="1" style="1" min="2" max="3"/>
-    <col width="8.88671875" customWidth="1" style="1" min="4" max="16384"/>
+    <col width="18.44140625" bestFit="1" customWidth="1" style="22" min="1" max="1"/>
+    <col width="13.44140625" bestFit="1" customWidth="1" style="22" min="2" max="3"/>
+    <col width="8.88671875" customWidth="1" style="22" min="4" max="4"/>
+    <col width="8.88671875" customWidth="1" style="22" min="5" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="3">
@@ -513,11 +515,11 @@
         </is>
       </c>
       <c r="B2" s="7">
-        <f>Stocks!$J$16</f>
+        <f>Stocks!$J$15</f>
         <v/>
       </c>
       <c r="C2" s="12">
-        <f>Stocks!$F$16</f>
+        <f>Stocks!$F$15</f>
         <v/>
       </c>
     </row>
@@ -551,7 +553,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" customFormat="1" s="13">
+    <row r="5" customFormat="1" s="20">
       <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -566,13 +568,13 @@
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="1" s="13">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" customFormat="1" s="20">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>% Upside/Downside</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f>(B5-C5)/C5</f>
         <v/>
       </c>
@@ -591,25 +593,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="6.5546875" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.21875" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="18.33203125" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="13.77734375" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
-    <col width="11.109375" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
-    <col width="10.44140625" customWidth="1" style="1" min="9" max="9"/>
-    <col width="15.77734375" customWidth="1" style="1" min="10" max="10"/>
-    <col width="15.6640625" bestFit="1" customWidth="1" style="1" min="11" max="11"/>
-    <col width="14.88671875" bestFit="1" customWidth="1" style="1" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="1" min="13" max="13"/>
-    <col width="12.33203125" bestFit="1" customWidth="1" style="1" min="14" max="14"/>
-    <col width="11.5546875" customWidth="1" style="1" min="15" max="15"/>
-    <col width="8.88671875" customWidth="1" style="1" min="16" max="16384"/>
+    <col width="20.21875" bestFit="1" customWidth="1" style="22" min="2" max="2"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="22" min="3" max="3"/>
+    <col width="18.33203125" bestFit="1" customWidth="1" style="22" min="4" max="4"/>
+    <col width="13.77734375" bestFit="1" customWidth="1" style="22" min="5" max="5"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="22" min="6" max="6"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="22" min="7" max="7"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" style="22" min="8" max="8"/>
+    <col width="10.44140625" customWidth="1" style="22" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" style="22" min="10" max="10"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="22" min="11" max="11"/>
+    <col width="14.88671875" bestFit="1" customWidth="1" style="22" min="12" max="12"/>
+    <col width="8.88671875" customWidth="1" style="22" min="13" max="13"/>
+    <col width="12.33203125" bestFit="1" customWidth="1" style="22" min="14" max="14"/>
+    <col width="11.5546875" customWidth="1" style="22" min="15" max="15"/>
+    <col width="8.88671875" customWidth="1" style="22" min="16" max="16"/>
+    <col width="8.88671875" customWidth="1" style="22" min="17" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.6" customFormat="1" customHeight="1" s="11">
@@ -703,14 +706,24 @@
           <t>HDFC BANK</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>693.7</v>
+      </c>
       <c r="F2" s="7">
         <f>D2*E2</f>
         <v/>
       </c>
-      <c r="G2" s="7" t="n"/>
+      <c r="G2" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="H2" s="7">
         <f>F2+G2</f>
         <v/>
@@ -742,23 +755,33 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="7" t="n"/>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1157.9</v>
+      </c>
       <c r="F3" s="7">
         <f>D3*E3</f>
         <v/>
       </c>
-      <c r="G3" s="7" t="n"/>
+      <c r="G3" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="H3" s="7">
         <f>F3+G3</f>
         <v/>
       </c>
       <c r="I3" s="7" t="n">
-        <v>2530</v>
+        <v>1164.9</v>
       </c>
       <c r="J3" s="7">
         <f>(D3-L3)*I3</f>
@@ -784,23 +807,33 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
+          <t>VARUN BEVERAGES</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>399.45</v>
+      </c>
       <c r="F4" s="7">
         <f>D4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="7" t="n"/>
+      <c r="G4" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="H4" s="7">
         <f>F4+G4</f>
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>1190</v>
+        <v>392</v>
       </c>
       <c r="J4" s="7">
         <f>(D4-L4)*I4</f>
@@ -824,11 +857,7 @@
         <f>A4+1</f>
         <v/>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>VARUN BEVERAGES</t>
-        </is>
-      </c>
+      <c r="B5" s="6" t="n"/>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="6" t="n"/>
       <c r="E5" s="7" t="n"/>
@@ -841,9 +870,7 @@
         <f>F5+G5</f>
         <v/>
       </c>
-      <c r="I5" s="7" t="n">
-        <v>395.1</v>
-      </c>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7">
         <f>(D5-L5)*I5</f>
         <v/>
@@ -1150,88 +1177,52 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
-        <f>A13+1</f>
-        <v/>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7">
-        <f>F14+G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7">
-        <f>(D14-L14)*I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="7">
-        <f>(L14*M14)-N14</f>
-        <v/>
-      </c>
-      <c r="P14" s="12">
-        <f>O14-(L14*E14)</f>
-        <v/>
-      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F15" s="4">
+        <f>SUM(F2:F14)</f>
+        <v/>
+      </c>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="H15" s="4">
+        <f>SUM(H2:H14)</f>
+        <v/>
+      </c>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="4">
+        <f>SUM(J2:J14)</f>
+        <v/>
+      </c>
+      <c r="P15" s="4">
+        <f>SUM(P2:P14)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="F16" s="4">
-        <f>SUM(F2:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4">
-        <f>SUM(H2:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4">
-        <f>SUM(J2:J15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="4">
-        <f>SUM(P2:P15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="21" t="inlineStr">
-        <is>
           <t>% upside/downside</t>
         </is>
       </c>
-      <c r="F17" s="16">
-        <f>(J16-F16)/F16</f>
+      <c r="F16" s="16">
+        <f>(J15-F15)/F15</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1247,7 +1238,8 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.21875" defaultRowHeight="13.8"/>
   <cols>
-    <col width="13.21875" customWidth="1" style="1" min="1" max="16384"/>
+    <col width="13.21875" customWidth="1" style="22" min="1" max="1"/>
+    <col width="13.21875" customWidth="1" style="22" min="2" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="41.4" customHeight="1">
@@ -1341,9 +1333,17 @@
           <t>TATASIL</t>
         </is>
       </c>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="7" t="n"/>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>17.73</v>
+      </c>
       <c r="F2" s="7">
         <f>D2*E2</f>
         <v/>
@@ -1354,7 +1354,7 @@
         <v/>
       </c>
       <c r="I2" s="7" t="n">
-        <v>18.69</v>
+        <v>17.65</v>
       </c>
       <c r="J2" s="7">
         <f>(D2-L2)*I2</f>
@@ -1383,9 +1383,17 @@
           <t>TATAGOLD</t>
         </is>
       </c>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="6" t="n"/>
-      <c r="E3" s="7" t="n"/>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>369</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>13.58</v>
+      </c>
       <c r="F3" s="7">
         <f>D3*E3</f>
         <v/>
@@ -1396,7 +1404,7 @@
         <v/>
       </c>
       <c r="I3" s="7" t="n">
-        <v>13.63</v>
+        <v>13.56</v>
       </c>
       <c r="J3" s="7">
         <f>(D3-L3)*I3</f>
@@ -1425,9 +1433,17 @@
           <t>NIFTYBEES</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>30-10-2026</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>263.09</v>
+      </c>
       <c r="F4" s="7">
         <f>D4*E4</f>
         <v/>
@@ -1438,7 +1454,7 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>257.22</v>
+        <v>262.89</v>
       </c>
       <c r="J4" s="7">
         <f>(D4-L4)*I4</f>
@@ -1558,9 +1574,10 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.21875" defaultRowHeight="13.8"/>
   <cols>
-    <col width="13.21875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="24.44140625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="13.21875" customWidth="1" style="1" min="3" max="16384"/>
+    <col width="13.21875" customWidth="1" style="22" min="1" max="1"/>
+    <col width="24.44140625" bestFit="1" customWidth="1" style="22" min="2" max="2"/>
+    <col width="13.21875" customWidth="1" style="22" min="3" max="3"/>
+    <col width="13.21875" customWidth="1" style="22" min="4" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="41.4" customHeight="1">
@@ -1622,15 +1639,15 @@
       <c r="C2" s="6" t="n">
         <v>801.022</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>103.61</v>
       </c>
       <c r="E2" s="7">
         <f>C2*D2</f>
         <v/>
       </c>
-      <c r="F2" s="18" t="n">
-        <v>124.67</v>
+      <c r="F2" s="17" t="n">
+        <v>129.09</v>
       </c>
       <c r="G2" s="7">
         <f>C2*F2</f>
@@ -1640,8 +1657,8 @@
         <f>G2-E2</f>
         <v/>
       </c>
-      <c r="I2" s="19">
-        <f>H2/E2</f>
+      <c r="I2" s="18">
+        <f>IF(E2&gt;0, H2/E2, 0)</f>
         <v/>
       </c>
     </row>
@@ -1658,15 +1675,15 @@
       <c r="C3" s="6" t="n">
         <v>1048.87</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="17" t="n">
         <v>76.75</v>
       </c>
       <c r="E3" s="7">
         <f>C3*D3</f>
         <v/>
       </c>
-      <c r="F3" s="18" t="n">
-        <v>88.9695</v>
+      <c r="F3" s="17" t="n">
+        <v>88.9623</v>
       </c>
       <c r="G3" s="7">
         <f>C3*F3</f>
@@ -1676,8 +1693,8 @@
         <f>G3-E3</f>
         <v/>
       </c>
-      <c r="I3" s="19">
-        <f>H3/E3</f>
+      <c r="I3" s="18">
+        <f>IF(E3&gt;0, H3/E3, 0)</f>
         <v/>
       </c>
     </row>
@@ -1694,15 +1711,15 @@
       <c r="C4" s="6" t="n">
         <v>8231.880999999999</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>10.08</v>
       </c>
       <c r="E4" s="7">
         <f>C4*D4</f>
         <v/>
       </c>
-      <c r="F4" s="18" t="n">
-        <v>9.2342</v>
+      <c r="F4" s="17" t="n">
+        <v>9.403600000000001</v>
       </c>
       <c r="G4" s="7">
         <f>C4*F4</f>
@@ -1712,8 +1729,8 @@
         <f>G4-E4</f>
         <v/>
       </c>
-      <c r="I4" s="19">
-        <f>H4/E4</f>
+      <c r="I4" s="18">
+        <f>IF(E4&gt;0, H4/E4, 0)</f>
         <v/>
       </c>
     </row>
@@ -1728,13 +1745,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
-      <c r="D5" s="18" t="n"/>
+      <c r="D5" s="17" t="n"/>
       <c r="E5" s="7">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>213.423</v>
+      <c r="F5" s="17" t="n">
+        <v>217.641</v>
       </c>
       <c r="G5" s="7">
         <f>C5*F5</f>
@@ -1744,8 +1761,8 @@
         <f>G5-E5</f>
         <v/>
       </c>
-      <c r="I5" s="19">
-        <f>H5/E5</f>
+      <c r="I5" s="18">
+        <f>IF(E5&gt;0, H5/E5, 0)</f>
         <v/>
       </c>
     </row>
@@ -1760,13 +1777,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="18" t="n"/>
+      <c r="D6" s="17" t="n"/>
       <c r="E6" s="7">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>387.1125</v>
+      <c r="F6" s="17" t="n">
+        <v>393.3366</v>
       </c>
       <c r="G6" s="7">
         <f>C6*F6</f>
@@ -1776,8 +1793,8 @@
         <f>G6-E6</f>
         <v/>
       </c>
-      <c r="I6" s="19">
-        <f>H6/E6</f>
+      <c r="I6" s="18">
+        <f>IF(E6&gt;0, H6/E6, 0)</f>
         <v/>
       </c>
     </row>
@@ -1816,7 +1833,7 @@
           <t>% upside/downside</t>
         </is>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <f>H8/E8</f>
         <v/>
       </c>
